--- a/templates/입고주문-템플릿-임포트.xlsx
+++ b/templates/입고주문-템플릿-임포트.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10208"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64F35AC-BCC0-7B46-B757-4275826FDE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC398F4-3264-054E-818F-59922DFEEE24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33080" yWindow="2720" windowWidth="27620" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,7 +13,7 @@
   <definedNames>
     <definedName name="barcode">'입고주문 현황'!#REF!</definedName>
     <definedName name="bl_no">'입고주문 현황'!#REF!</definedName>
-    <definedName name="box_wt">'입고주문 현황'!$O$1</definedName>
+    <definedName name="box_wt">'입고주문 현황'!$P$1</definedName>
     <definedName name="car_no">'입고주문 현황'!#REF!</definedName>
     <definedName name="com_cd">'입고주문 현황'!$B$1</definedName>
     <definedName name="created_at">'입고주문 현황'!#REF!</definedName>
@@ -24,19 +24,19 @@
     <definedName name="exp_box_qty">'입고주문 현황'!#REF!</definedName>
     <definedName name="exp_ea_qty">'입고주문 현황'!#REF!</definedName>
     <definedName name="exp_pallet_qty">'입고주문 현황'!#REF!</definedName>
-    <definedName name="expired_date">'입고주문 현황'!$L$1</definedName>
+    <definedName name="expired_date">'입고주문 현황'!$M$1</definedName>
     <definedName name="id">'입고주문 현황'!#REF!</definedName>
     <definedName name="insp_flag">'입고주문 현황'!#REF!</definedName>
     <definedName name="insp_qty">'입고주문 현황'!#REF!</definedName>
     <definedName name="invoice_no">'입고주문 현황'!$I$1</definedName>
-    <definedName name="item_remarks">'입고주문 현황'!$R$1</definedName>
+    <definedName name="item_remarks">'입고주문 현황'!$S$1</definedName>
     <definedName name="item_type">'입고주문 현황'!#REF!</definedName>
     <definedName name="label_flag">'입고주문 현황'!#REF!</definedName>
     <definedName name="line_remarks">'입고주문 현황'!#REF!</definedName>
     <definedName name="line_status">'입고주문 현황'!#REF!</definedName>
     <definedName name="loc_cd">'입고주문 현황'!#REF!</definedName>
-    <definedName name="lot_no">'입고주문 현황'!$M$1</definedName>
-    <definedName name="mgr_id">'입고주문 현황'!$P$1</definedName>
+    <definedName name="lot_no">'입고주문 현황'!$N$1</definedName>
+    <definedName name="mgr_id">'입고주문 현황'!$Q$1</definedName>
     <definedName name="mgr_iod">'입고주문 현황'!#REF!</definedName>
     <definedName name="origin">'입고주문 현황'!$J$1</definedName>
     <definedName name="owner">'입고주문 현황'!#REF!</definedName>
@@ -46,8 +46,8 @@
     <definedName name="rcv_date">'입고주문 현황'!#REF!</definedName>
     <definedName name="rcv_ea_qty">'입고주문 현황'!#REF!</definedName>
     <definedName name="rcv_end_date">'입고주문 현황'!#REF!</definedName>
-    <definedName name="rcv_exp_date">'입고주문 현황'!#REF!</definedName>
-    <definedName name="rcv_exp_qty">'입고주문 현황'!$K$1</definedName>
+    <definedName name="rcv_exp_date">'입고주문 현황'!$K$1</definedName>
+    <definedName name="rcv_exp_qty">'입고주문 현황'!$L$1</definedName>
     <definedName name="rcv_exp_seq">'입고주문 현황'!#REF!</definedName>
     <definedName name="rcv_no">'입고주문 현황'!#REF!</definedName>
     <definedName name="rcv_pallet_qty">'입고주문 현황'!#REF!</definedName>
@@ -58,11 +58,11 @@
     <definedName name="rcv_type">'입고주문 현황'!$F$1</definedName>
     <definedName name="release_invoice">'입고주문 현황'!#REF!</definedName>
     <definedName name="release_no">'입고주문 현황'!$H$1</definedName>
-    <definedName name="release_seq">'입고주문 현황'!$P$1</definedName>
-    <definedName name="remarks">'입고주문 현황'!$Q$1</definedName>
+    <definedName name="release_seq">'입고주문 현황'!$Q$1</definedName>
+    <definedName name="remarks">'입고주문 현황'!$R$1</definedName>
     <definedName name="sku_cd">'입고주문 현황'!$G$1</definedName>
     <definedName name="status">'입고주문 현황'!#REF!</definedName>
-    <definedName name="total_box">'입고주문 현황'!$N$1</definedName>
+    <definedName name="total_box">'입고주문 현황'!$O$1</definedName>
     <definedName name="total_exp_qty">'입고주문 현황'!#REF!</definedName>
     <definedName name="trace1_cd">'입고주문 현황'!#REF!</definedName>
     <definedName name="trace2_cd">'입고주문 현황'!#REF!</definedName>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="27">
   <si>
     <t>입고요청일</t>
   </si>
@@ -213,12 +213,16 @@
     <t>WH001</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>입고예정일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -281,6 +285,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Malgun Gothic"/>
+      <family val="1"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -323,7 +335,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
@@ -351,6 +363,9 @@
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -692,16 +707,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5" style="1"/>
-    <col min="12" max="12" width="14.5" style="1"/>
+    <col min="13" max="13" width="14.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="18">
+    <row r="1" spans="1:19" ht="18">
       <c r="A1" s="7" t="s">
         <v>2</v>
       </c>
@@ -732,32 +747,35 @@
       <c r="J1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="N1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="O1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="P1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="Q1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="R1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="S1" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:19">
       <c r="A2" s="2" t="s">
         <v>25</v>
       </c>
@@ -786,20 +804,21 @@
         <v>9181953110</v>
       </c>
       <c r="J2" s="3"/>
-      <c r="K2" s="6">
+      <c r="K2" s="3"/>
+      <c r="L2" s="6">
         <v>17000</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="M2" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="5"/>
-      <c r="N2" s="3"/>
+      <c r="N2" s="5"/>
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
-      <c r="Q2" s="5"/>
+      <c r="Q2" s="3"/>
       <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:19">
       <c r="A3" s="2" t="s">
         <v>25</v>
       </c>
@@ -828,20 +847,21 @@
         <v>9181953110</v>
       </c>
       <c r="J3" s="3"/>
-      <c r="K3" s="6">
+      <c r="K3" s="3"/>
+      <c r="L3" s="6">
         <v>17000</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="M3" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="5"/>
-      <c r="N3" s="3"/>
+      <c r="N3" s="5"/>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
-      <c r="Q3" s="5"/>
+      <c r="Q3" s="3"/>
       <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:19">
       <c r="A4" s="2" t="s">
         <v>25</v>
       </c>
@@ -870,23 +890,24 @@
         <v>9181953110</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="6">
+      <c r="K4" s="3"/>
+      <c r="L4" s="6">
         <v>40000</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="M4" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M4" s="5"/>
-      <c r="N4" s="3"/>
+      <c r="N4" s="5"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
-      <c r="Q4" s="5"/>
+      <c r="Q4" s="3"/>
       <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="decimal" allowBlank="1" sqref="K2:K4" xr:uid="{D8D5C67B-27CE-B943-AD31-845C948DD471}"/>
+    <dataValidation type="decimal" allowBlank="1" sqref="L2:L4" xr:uid="{D8D5C67B-27CE-B943-AD31-845C948DD471}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
